--- a/content/exercise_files/WorkerSatisfaction_Unprocessed_KEY.xlsx
+++ b/content/exercise_files/WorkerSatisfaction_Unprocessed_KEY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubcca-my.sharepoint.com/personal/vchoy01_student_ubc_ca/Documents/GAA_RDM/Workshops/07_Data_Anonymization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="11_D60AC8706D05C1D06CB00A851CF0927E1A9C67B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{618BC098-47F3-F247-85A7-A1E2BF73FD41}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_D60AC8706D05C1D06CB00A851CF0927E1A9C67B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608DCAA5-B05E-AE46-84DC-3ACB3DA1C0CA}"/>
   <bookViews>
-    <workbookView xWindow="16520" yWindow="7600" windowWidth="32040" windowHeight="20500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="8300" windowWidth="32040" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unprocessed data" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -546,6 +546,7 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5527,7 +5528,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -5575,7 +5576,7 @@
       <c r="G2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="15" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="15" t="s">
@@ -5613,7 +5614,7 @@
       <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="15" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="15" t="s">
@@ -5651,7 +5652,7 @@
       <c r="G4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="15" t="s">
         <v>24</v>
       </c>
       <c r="I4" s="15" t="s">
@@ -5688,7 +5689,7 @@
       <c r="G5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="15" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="15" t="s">
@@ -5726,7 +5727,7 @@
       <c r="G6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="15" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="15" t="s">
@@ -5764,7 +5765,7 @@
       <c r="G7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="15" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="15" t="s">
@@ -5802,7 +5803,7 @@
       <c r="G8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="15" t="s">
@@ -5840,7 +5841,7 @@
       <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="15" t="s">
@@ -5878,7 +5879,7 @@
       <c r="G10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="15" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="15" t="s">
@@ -5916,7 +5917,7 @@
       <c r="G11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="15" t="s">
         <v>46</v>
       </c>
       <c r="I11" s="15" t="s">
@@ -10244,7 +10245,7 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -10292,7 +10293,7 @@
       <c r="G2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="23" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="9" t="s">
@@ -10330,7 +10331,7 @@
       <c r="G3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="23" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="9" t="s">
@@ -10368,7 +10369,7 @@
       <c r="G4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="23" t="s">
         <v>24</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -10405,7 +10406,7 @@
       <c r="G5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="23" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -10443,7 +10444,7 @@
       <c r="G6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="23" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="9" t="s">
@@ -10481,7 +10482,7 @@
       <c r="G7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="23" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="9" t="s">
@@ -10519,7 +10520,7 @@
       <c r="G8" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="23" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="9" t="s">
@@ -10557,7 +10558,7 @@
       <c r="G9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="23" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -10595,7 +10596,7 @@
       <c r="G10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I10" s="9" t="s">
@@ -10633,7 +10634,7 @@
       <c r="G11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I11" s="9" t="s">
